--- a/data/GLD_lithic_coord.xlsx
+++ b/data/GLD_lithic_coord.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Geluo_cave_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9AE513-7924-4870-A089-4B4B425296C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E00A617-3BF2-4282-8A8C-1F486D8F8F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="351">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1083,6 +1083,14 @@
   </si>
   <si>
     <t>T1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stone_artifact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fossil</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1583,7 +1591,7 @@
         <v>2070.0210999999999</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -2623,7 +2631,7 @@
         <v>2069.2914000000001</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
